--- a/ejercicios/Semana7/casos_de_prueba.xlsx
+++ b/ejercicios/Semana7/casos_de_prueba.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos Esteban\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos Esteban\Documents\GitRepos\C3-2026-SCV6\ejercicios\Semana7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F838774C-94F8-4746-B4B1-5F64921794C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB3187-E262-41C8-9EB7-7053E47F73EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{9DD57C2C-1553-42D1-AA2F-9C96E2F8B2F4}"/>
+    <workbookView xWindow="4155" yWindow="4035" windowWidth="38700" windowHeight="15345" xr2:uid="{9DD57C2C-1553-42D1-AA2F-9C96E2F8B2F4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Casos de Prueba" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabla de Traza" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>N.º</t>
   </si>
@@ -127,12 +128,6 @@
 Balance final ₡202510.00</t>
   </si>
   <si>
-    <t>Sin líneas de mes dentro del ciclo.
-months = 0.
-“Se alcanzó la meta de ahorro en el mes 0”.
-Balance final ₡200000.00</t>
-  </si>
-  <si>
     <t>Una vuelta: 100000 + 1000 + 50000 = 151000, que es mayor o igual a la meta, y el ciclo sale</t>
   </si>
   <si>
@@ -219,14 +214,6 @@
 Balance Final: ₡202510.00</t>
   </si>
   <si>
-    <t>Ahorro inicial (₡): 200000
-Aporte mensual (₡): 10000
-Tasa de interés mensual (%): 1
-Meta de ahorro (₡): 150000
-Se alcanzó la meta de ahorro en el mes 0
-Balance Final: ₡200000.00</t>
-  </si>
-  <si>
     <t>Tasa de interés mensual (%): 1
 Meta de ahorro (₡): 150000
 Meses de Ahorro: 1
@@ -235,26 +222,114 @@
 Balance Final: ₡151000.00</t>
   </si>
   <si>
-    <t>Balance de Ahorro: ₡200000.00
+    <t xml:space="preserve">Balance de Ahorro: ₡200000.00
 Se alcanzó la meta de ahorro en el mes 10
 Balance Final: ₡200000.00
-PS C:\Users\Carlos Esteban\</t>
+</t>
+  </si>
+  <si>
+    <t>Sin líneas de mes dentro del ciclo.
+months = 0.
+“El ahorro ya cumple la meta”.
+Balance final ₡200000.00</t>
+  </si>
+  <si>
+    <t>Ahorro inicial (₡): 200000
+Aporte mensual (₡): 10000
+Tasa de interés mensual (%): 1
+Meta de ahorro (₡): 150000
+El ahorro ya cumple la meta
+Balance Final: ₡200000.00</t>
+  </si>
+  <si>
+    <t>Iteración</t>
+  </si>
+  <si>
+    <t>Variables de control (antes)</t>
+  </si>
+  <si>
+    <t>Condición evaluada</t>
+  </si>
+  <si>
+    <t>¿Entra al ciclo?</t>
+  </si>
+  <si>
+    <t>Cálculos / actualizaciones</t>
+  </si>
+  <si>
+    <t>Acumuladores (después)</t>
+  </si>
+  <si>
+    <t>Salida mostrada</t>
+  </si>
+  <si>
+    <t>balance = 100000
+months = 0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>100000 &lt; 160000 and 0 &lt; 120</t>
+  </si>
+  <si>
+    <t>balance = 101000
+balance = 151000
+months = 1</t>
+  </si>
+  <si>
+    <t>balance = 151000
+months = 1</t>
+  </si>
+  <si>
+    <t>Meses de Ahorro: 1
+Balance de Ahorro: ₡151000.00</t>
+  </si>
+  <si>
+    <t>151000&lt; 160000 and 1 &lt; 120</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>balance = 202510
+months = 2</t>
+  </si>
+  <si>
+    <t>Meses de Ahorro: 2
+Balance de Ahorro: ₡202510.00</t>
+  </si>
+  <si>
+    <t>balance = 152510
+balance = 202510
+months = 2</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>202510&lt; 160000 and 2 &lt; 120</t>
+  </si>
+  <si>
+    <t>Se alcanzó la meta de ahorro en el mes 2
+Balance Final: ₡202510.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -266,16 +341,42 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E2A4A"/>
+        <bgColor rgb="FF1E2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -298,21 +399,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -320,8 +430,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,247 +782,362 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="93.75" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="105">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="105">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="G4" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="90.75" customHeight="1">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="182.25" customHeight="1">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="105">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="90.75" customHeight="1">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="95.25" customHeight="1">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1">
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1">
-      <c r="F15"/>
-      <c r="G15"/>
-    </row>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1"/>
     <row r="16" spans="1:7">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16"/>
-      <c r="G16"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17"/>
-      <c r="G17"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18"/>
-      <c r="G18"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B892244-7242-4903-938D-2F852EF521DD}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="56.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="34.85546875" customWidth="1"/>
+    <col min="7" max="7" width="47.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="56.25" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="56.25" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="56.25" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A2:A3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/ejercicios/Semana7/casos_de_prueba.xlsx
+++ b/ejercicios/Semana7/casos_de_prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos Esteban\Documents\GitRepos\C3-2026-SCV6\ejercicios\Semana7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB3187-E262-41C8-9EB7-7053E47F73EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3981107-9C7E-4035-AFB5-C942CAC86DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="4035" windowWidth="38700" windowHeight="15345" xr2:uid="{9DD57C2C-1553-42D1-AA2F-9C96E2F8B2F4}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{9DD57C2C-1553-42D1-AA2F-9C96E2F8B2F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de Prueba" sheetId="1" r:id="rId1"/>
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -436,14 +436,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,25 +795,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1023,35 +1026,35 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="56.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
-    <col min="6" max="6" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
     <col min="7" max="7" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" s="10" customFormat="1" ht="45">
+      <c r="A1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1062,7 +1065,7 @@
       <c r="B2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1079,13 +1082,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1108,7 +1111,7 @@
       <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
